--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484542_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484542_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7248</v>
+        <v>0.8619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9305</v>
+        <v>0.2163</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7942</v>
+        <v>0.6456</v>
       </c>
       <c r="G2" t="n">
         <v>0.4754</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0374</v>
+        <v>0.1746</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2361</v>
+        <v>-0.4781</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8013</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.945</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4251</v>
+        <v>0.6229</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.6923</v>
+        <v>-1.445</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1175</v>
+        <v>2.0679</v>
       </c>
       <c r="G3" t="n">
         <v>2.1799</v>
@@ -688,13 +688,13 @@
         <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2887</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9359</v>
+        <v>-0.6885</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6472</v>
+        <v>0.5976</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3629</v>
+        <v>0.5141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4836</v>
+        <v>-0.171</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1207</v>
+        <v>0.6851</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0377</v>
+        <v>1.1052</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1047</v>
+        <v>0.3067</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9330000000000001</v>
+        <v>0.7985</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2324</v>
+        <v>1.461</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4982</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7342</v>
+        <v>0.7024</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2701</v>
+        <v>-0.3558</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6029</v>
+        <v>-0.4519</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6673</v>
+        <v>0.0961</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0054</v>
+        <v>-0.5911</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6334</v>
+        <v>-0.7157</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6389</v>
+        <v>0.1246</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5785</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. LLOPIS FELIPO</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3276</v>
+        <v>0.4638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4182</v>
+        <v>1.1295</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0906</v>
+        <v>-0.6657</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1971</v>
+        <v>-1.0377</v>
       </c>
       <c r="H5" t="n">
-        <v>0.101</v>
+        <v>-0.1047</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0961</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4552</v>
+        <v>2.2324</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4552</v>
+        <v>1.4982</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.7342</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2581</v>
+        <v>-3.2701</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3541</v>
+        <v>-1.6029</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0961</v>
+        <v>-1.6673</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.236</v>
+        <v>0.1063</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0369</v>
+        <v>-0.9875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.199</v>
+        <v>1.0938</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.5785</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>V. LLOPIS FELIPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1866</v>
+        <v>0.399</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.226</v>
+        <v>0.5144</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4126</v>
+        <v>-0.1154</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1052</v>
+        <v>0.1971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3067</v>
+        <v>0.101</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7985</v>
+        <v>0.0961</v>
       </c>
       <c r="J6" t="n">
-        <v>1.461</v>
+        <v>0.4552</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.4552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7024</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3558</v>
+        <v>-0.2581</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4519</v>
+        <v>-0.3541</v>
       </c>
       <c r="O6" t="n">
         <v>0.0961</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9163</v>
+        <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9186</v>
+        <v>-0.1646</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.0592</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1479</v>
+        <v>-0.2238</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5122</v>
+        <v>-0.7427</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.229</v>
+        <v>-0.5586</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2832</v>
+        <v>-0.1841</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3499</v>
@@ -1000,13 +1000,13 @@
         <v>0.3665</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3587</v>
+        <v>0.1282</v>
       </c>
       <c r="T7" t="n">
-        <v>0.549</v>
+        <v>0.2195</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1903</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. HYLLA</t>
+          <t>J. JODAR SAIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0608</v>
+        <v>-3.3698</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6579</v>
+        <v>-1.6714</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4029</v>
+        <v>-1.6984</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8277</v>
+        <v>-2.2426</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1822</v>
+        <v>-0.986</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0099</v>
+        <v>-1.2566</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0043</v>
+        <v>-0.1726</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2446</v>
+        <v>-0.1983</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2404</v>
+        <v>0.0258</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.832</v>
+        <v>-2.07</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0624</v>
+        <v>-0.7876</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7695</v>
+        <v>-1.2824</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.733</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.0995</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.3665</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.9163</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2828</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.9344</v>
+        <v>-0.3942</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2542</v>
+        <v>-0.3993</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6802</v>
+        <v>0.0051</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JODAR SAIZ</t>
+          <t>L. HYLLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6449</v>
+        <v>-3.8715</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8226</v>
+        <v>-1.2208</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8223</v>
+        <v>-2.6506</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2426</v>
+        <v>-1.8277</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.986</v>
+        <v>0.1822</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2566</v>
+        <v>-2.0099</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1726</v>
+        <v>0.0043</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1983</v>
+        <v>1.2446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0258</v>
+        <v>-1.2404</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.07</v>
+        <v>-1.832</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7876</v>
+        <v>-1.0624</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2824</v>
+        <v>-0.7695</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6693</v>
+        <v>0.1237</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5505</v>
+        <v>-0.3088</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1188</v>
+        <v>0.4325</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6324</v>
+        <v>-4.107</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4757</v>
+        <v>-3.1733</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1567</v>
+        <v>-0.9337</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3987</v>
@@ -1234,13 +1234,13 @@
         <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9509</v>
+        <v>-0.4255</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.046</v>
+        <v>-0.7436</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0951</v>
+        <v>0.318</v>
       </c>
       <c r="V10" t="n">
         <v>-1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0547</v>
+        <v>-5.34</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0275</v>
+        <v>-0.4366</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0273</v>
+        <v>-4.9034</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9328</v>
@@ -1312,13 +1312,13 @@
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9808</v>
+        <v>-0.266</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3582</v>
+        <v>-0.7673</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3774</v>
+        <v>0.5013</v>
       </c>
       <c r="V11" t="n">
         <v>-3.7905</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9552</v>
+        <v>-6.4383</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5043</v>
+        <v>-4.1608</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4509</v>
+        <v>-2.2774</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7851</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2147</v>
+        <v>0.3022</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.4272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.556</v>
+        <v>0.7294</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5889</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.8332</v>
+        <v>-21.0076</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.803</v>
+        <v>-10.9773</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.0303</v>
+        <v>-10.0301</v>
       </c>
       <c r="G13" t="n">
         <v>-9.616899999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0001000000000003221</v>
+        <v>9.999999999987796e-05</v>
       </c>
       <c r="I13" t="n">
         <v>-9.6168</v>
@@ -1468,13 +1468,13 @@
         <v>10.9954</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9231</v>
+        <v>-1.0973</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.063</v>
+        <v>-5.237299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1401</v>
+        <v>4.139900000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-5.7118</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0077</v>
+        <v>6.7731</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6632</v>
+        <v>3.3747</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3445</v>
+        <v>3.3984</v>
       </c>
       <c r="G14" t="n">
         <v>6.6357</v>
@@ -1546,13 +1546,13 @@
         <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9218</v>
+        <v>0.6872</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1493</v>
+        <v>-0.4378</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0711</v>
+        <v>1.125</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9016</v>
+        <v>6.5339</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4404</v>
+        <v>2.825</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4612</v>
+        <v>3.7089</v>
       </c>
       <c r="G15" t="n">
         <v>2.5955</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5498</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.5332</v>
       </c>
       <c r="U15" t="n">
-        <v>0.368</v>
+        <v>0.6157</v>
       </c>
       <c r="V15" t="n">
         <v>3.4894</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>J. ROBERTO JUREVICIUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.748</v>
+        <v>3.8779</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5496</v>
+        <v>1.9348</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1984</v>
+        <v>1.9431</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4644</v>
+        <v>0.3833</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3178</v>
+        <v>1.0275</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7821</v>
+        <v>-0.6442</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2751</v>
+        <v>0.2735</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7491</v>
+        <v>1.4305</v>
       </c>
       <c r="L16" t="n">
-        <v>1.526</v>
+        <v>-1.157</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8107</v>
+        <v>0.1098</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0668</v>
+        <v>-0.403</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2561</v>
+        <v>0.5128</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3123</v>
+        <v>0.4397</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1312</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4435</v>
+        <v>0.3673</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROBERTO JUREVICIUS</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3942</v>
+        <v>3.8107</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5502</v>
+        <v>2.2611</v>
       </c>
       <c r="F17" t="n">
-        <v>1.844</v>
+        <v>1.5495</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3833</v>
+        <v>1.4644</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0275</v>
+        <v>-0.3178</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6442</v>
+        <v>1.7821</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2735</v>
+        <v>3.2751</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4305</v>
+        <v>1.7491</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.157</v>
+        <v>1.526</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1098</v>
+        <v>-1.8107</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.403</v>
+        <v>-2.0668</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5128</v>
+        <v>0.2561</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.044</v>
+        <v>0.375</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3122</v>
+        <v>-0.4196</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2682</v>
+        <v>0.7947</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1541</v>
+        <v>2.2115</v>
       </c>
       <c r="E18" t="n">
-        <v>3.155</v>
+        <v>2.3858</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0009</v>
+        <v>-0.1743</v>
       </c>
       <c r="G18" t="n">
         <v>1.7615</v>
@@ -1858,13 +1858,13 @@
         <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4606</v>
+        <v>0.5179</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4744</v>
+        <v>-0.2949</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9862</v>
+        <v>0.8128</v>
       </c>
       <c r="V18" t="n">
         <v>-1.9005</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5065</v>
+        <v>1.9218</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7733</v>
+        <v>0.9656</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7332</v>
+        <v>0.9562</v>
       </c>
       <c r="G19" t="n">
         <v>0.1912</v>
@@ -1936,13 +1936,13 @@
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9516</v>
+        <v>-0.5364</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3212</v>
+        <v>-1.1289</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3696</v>
+        <v>0.5926</v>
       </c>
       <c r="V19" t="n">
         <v>1.9005</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>E. CAMPOS MONTEIRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8021</v>
+        <v>0.7109</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8102</v>
+        <v>1.2251</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6123</v>
+        <v>-0.5142</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5882</v>
+        <v>0.7247</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0014</v>
+        <v>-0.6954</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5868</v>
+        <v>1.4201</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0431</v>
+        <v>1.3353</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6716</v>
+        <v>0.0433</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7147</v>
+        <v>1.2919</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5451</v>
+        <v>-0.6106</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.673</v>
+        <v>-0.7388</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1279</v>
+        <v>0.1282</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8014</v>
+        <v>-0.197</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8454</v>
+        <v>-0.1101</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6468</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. CAMPOS MONTEIRO</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6862</v>
+        <v>0.7015</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2251</v>
+        <v>-0.6179</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.539</v>
+        <v>1.3194</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7247</v>
+        <v>-1.5882</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6954</v>
+        <v>-0.0014</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4201</v>
+        <v>-1.5868</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3353</v>
+        <v>-0.0431</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0433</v>
+        <v>1.6716</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2919</v>
+        <v>-1.7147</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6106</v>
+        <v>-1.5451</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7388</v>
+        <v>-1.673</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1282</v>
+        <v>0.1279</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1833</v>
+        <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2218</v>
+        <v>0.7008</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1101</v>
+        <v>-0.6531</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1117</v>
+        <v>1.3539</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5986</v>
+        <v>-1.4545</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4877</v>
+        <v>-2.1992</v>
       </c>
       <c r="F22" t="n">
-        <v>0.889</v>
+        <v>0.7447</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2428</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.2385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5347</v>
+        <v>0.3904</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7685</v>
+        <v>-2.6126</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0288</v>
+        <v>-2.1249</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7398</v>
+        <v>-0.4877</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3083</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0999</v>
+        <v>0.2559</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3869</v>
+        <v>-0.483</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4868</v>
+        <v>0.7389</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2774</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.8333</v>
+        <v>22.4742</v>
       </c>
       <c r="E24" t="n">
         <v>10.0301</v>
       </c>
       <c r="F24" t="n">
-        <v>11.8029</v>
+        <v>12.444</v>
       </c>
       <c r="G24" t="n">
         <v>9.617000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>15.5771</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9231</v>
+        <v>2.5642</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.1401</v>
+        <v>-4.1402</v>
       </c>
       <c r="U24" t="n">
-        <v>6.0632</v>
+        <v>6.7044</v>
       </c>
       <c r="V24" t="n">
         <v>5.7117</v>
